--- a/project/outputs_xlsx_solution/test_new4.4-wide-NR-4.xlsx
+++ b/project/outputs_xlsx_solution/test_new4.4-wide-NR-4.xlsx
@@ -826,7 +826,7 @@
         <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
@@ -835,9 +835,6 @@
         <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -861,7 +858,7 @@
         <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -870,9 +867,6 @@
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" t="s">
         <v>20</v>
       </c>
     </row>
@@ -963,12 +957,9 @@
         <v>21</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" t="s">
         <v>19</v>
       </c>
       <c r="Q11" t="s">
@@ -991,16 +982,13 @@
       <c r="G12" t="s">
         <v>9</v>
       </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M12" t="s">
-        <v>24</v>
-      </c>
-      <c r="N12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O12" t="s">
         <v>19</v>
       </c>
       <c r="Q12" t="s">
@@ -1023,6 +1011,9 @@
       <c r="G13" t="s">
         <v>9</v>
       </c>
+      <c r="L13" t="s">
+        <v>21</v>
+      </c>
       <c r="M13" t="s">
         <v>21</v>
       </c>
@@ -1416,12 +1407,9 @@
         <v>21</v>
       </c>
       <c r="AD26" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF26" t="s">
         <v>19</v>
       </c>
       <c r="AI26" t="s">
@@ -1628,12 +1616,9 @@
         <v>21</v>
       </c>
       <c r="AK33" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AL33" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM33" t="s">
         <v>19</v>
       </c>
       <c r="AP33" t="s">
@@ -1840,12 +1825,9 @@
         <v>21</v>
       </c>
       <c r="AR40" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AS40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT40" t="s">
         <v>19</v>
       </c>
       <c r="AW40" t="s">
